--- a/mock-data/logistics-master-data.xlsx
+++ b/mock-data/logistics-master-data.xlsx
@@ -523,7 +523,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>FastFreight</t>
+          <t>Midwest Freight</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>FastFreight</t>
+          <t>Midwest Freight</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>FastFreight</t>
+          <t>Midwest Freight</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -598,7 +598,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>FastFreight</t>
+          <t>Midwest Freight</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>ExpressCo</t>
+          <t>PrimeExpress</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -648,7 +648,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>ExpressCo</t>
+          <t>PrimeExpress</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>FastFreight</t>
+          <t>Midwest Freight</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -786,7 +786,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>FastFreight</t>
+          <t>Midwest Freight</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -810,7 +810,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>FastFreight</t>
+          <t>Midwest Freight</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -834,7 +834,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>ExpressCo</t>
+          <t>PrimeExpress</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>FastFreight,ExpressCo</t>
+          <t>Midwest Freight,PrimeExpress</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>FastFreight</t>
+          <t>Midwest Freight</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>FastFreight</t>
+          <t>Midwest Freight</t>
         </is>
       </c>
     </row>

--- a/mock-data/logistics-master-data.xlsx
+++ b/mock-data/logistics-master-data.xlsx
@@ -996,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1006,6 +1006,8 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1051,6 +1053,16 @@
           <t>carriers</t>
         </is>
       </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>supports_hazmat</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>priority_rank</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1088,6 +1100,14 @@
           <t>Midwest Freight,PrimeExpress</t>
         </is>
       </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1125,6 +1145,14 @@
           <t>Midwest Freight</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1162,10 +1190,18 @@
           <t>Midwest Freight</t>
         </is>
       </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mock-data/logistics-master-data.xlsx
+++ b/mock-data/logistics-master-data.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Midwest Freight</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Midwest Freight</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Midwest Freight</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -598,12 +598,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Midwest Freight</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>752</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -617,18 +617,18 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>PrimeExpress</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>900</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>EXPRESS</t>
+          <t>GROUND</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>PrimeExpress</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>902</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -663,35 +663,110 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>EXPRESS</t>
+          <t>GROUND</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>FedEx Express</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>EXPRESS</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>FedEx Express</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>EXPRESS</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>FedEx Express</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>EXPRESS</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>RegionalCarrier</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>GROUND</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -709,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -762,7 +837,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Midwest Freight</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -786,7 +861,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Midwest Freight</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -810,7 +885,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Midwest Freight</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -834,7 +909,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>PrimeExpress</t>
+          <t>FedEx Express</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -853,6 +928,30 @@
       </c>
       <c r="F6" s="4" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>FedEx Express</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Z2</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1196,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Midwest Freight,PrimeExpress</t>
+          <t>FedEx Freight,FedEx Express</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -1142,7 +1241,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Midwest Freight</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -1187,7 +1286,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Midwest Freight</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
